--- a/data/trans_dic/P1802_2016_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1802_2016_2023-Edad-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,59; 13,62</t>
+          <t>7,76; 13,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 13,67</t>
+          <t>4,32; 13,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,45; 18,18</t>
+          <t>11,18; 18,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,98; 16,4</t>
+          <t>8,35; 18,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,16; 14,84</t>
+          <t>10,37; 14,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 12,84</t>
+          <t>7,17; 13,8</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,47; 14,3</t>
+          <t>8,97; 14,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,97; 14,25</t>
+          <t>6,22; 13,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,43; 18,53</t>
+          <t>12,49; 18,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,21; 13,73</t>
+          <t>8,57; 14,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,3; 15,29</t>
+          <t>11,39; 15,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 13,12</t>
+          <t>8,39; 12,89</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,15; 16,66</t>
+          <t>11,17; 16,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,98; 21,78</t>
+          <t>13,33; 19,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,91; 18,79</t>
+          <t>13,04; 18,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,99; 18,08</t>
+          <t>12,79; 17,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,68; 16,44</t>
+          <t>12,59; 16,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,8; 19,05</t>
+          <t>13,59; 17,5</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,7; 19,96</t>
+          <t>13,97; 20,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,79; 74,9</t>
+          <t>13,52; 19,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,31; 19,16</t>
+          <t>13,48; 19,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,18; 23,06</t>
+          <t>19,24; 23,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,26; 18,55</t>
+          <t>14,29; 18,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,72; 58,68</t>
+          <t>17,11; 20,73</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,66; 19,47</t>
+          <t>12,41; 19,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,6; 24,2</t>
+          <t>17,0; 23,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,23; 30,68</t>
+          <t>22,13; 30,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,47; 28,81</t>
+          <t>23,01; 28,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,28; 23,69</t>
+          <t>18,23; 23,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,18; 25,38</t>
+          <t>21,09; 25,17</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,17; 20,95</t>
+          <t>12,78; 21,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,65; 22,13</t>
+          <t>15,24; 21,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,61; 30,01</t>
+          <t>20,27; 29,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,7; 22,41</t>
+          <t>18,64; 24,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,98; 24,14</t>
+          <t>17,94; 24,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,95; 20,77</t>
+          <t>17,88; 22,11</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,19; 22,8</t>
+          <t>14,5; 23,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,61; 19,6</t>
+          <t>12,52; 19,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,55; 29,18</t>
+          <t>19,47; 28,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,03; 23,29</t>
+          <t>17,66; 23,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,5; 25,39</t>
+          <t>18,59; 25,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,7; 21,06</t>
+          <t>16,4; 20,77</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,28; 15,7</t>
+          <t>13,19; 15,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,49; 39,25</t>
+          <t>13,94; 16,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,59; 20,25</t>
+          <t>17,52; 20,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,19; 18,84</t>
+          <t>17,7; 19,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,77; 17,69</t>
+          <t>15,76; 17,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,11; 29,79</t>
+          <t>16,12; 17,77</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30585</t>
+          <t>31677</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34987</t>
+          <t>45629</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65572</t>
+          <t>77307</t>
         </is>
       </c>
     </row>
@@ -1425,32 +1425,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31827; 57150</t>
+          <t>32531; 56553</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15906; 54674</t>
+          <t>17635; 54314</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45324; 71930</t>
+          <t>44237; 71576</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21869; 51370</t>
+          <t>30259; 66257</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>82794; 121012</t>
+          <t>84501; 120107</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43602; 91609</t>
+          <t>55259; 106337</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>43444</t>
+          <t>44993</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52032</t>
+          <t>56199</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95476</t>
+          <t>101192</t>
         </is>
       </c>
     </row>
@@ -1543,32 +1543,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49999; 84416</t>
+          <t>52997; 84734</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29517; 60347</t>
+          <t>29665; 63156</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70061; 104437</t>
+          <t>70395; 103324</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31769; 70204</t>
+          <t>42934; 70587</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>130461; 176473</t>
+          <t>131404; 176740</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72163; 122664</t>
+          <t>82072; 126080</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>97194</t>
+          <t>99226</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82707</t>
+          <t>93071</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>179901</t>
+          <t>192297</t>
         </is>
       </c>
     </row>
@@ -1661,32 +1661,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>74580; 111459</t>
+          <t>74754; 109972</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>80343; 116797</t>
+          <t>82727; 120913</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85390; 124293</t>
+          <t>86259; 122106</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70493; 98059</t>
+          <t>79551; 109157</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>168667; 218783</t>
+          <t>167441; 217850</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>159698; 205522</t>
+          <t>168890; 217520</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>352966</t>
+          <t>112993</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144950</t>
+          <t>159163</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>497916</t>
+          <t>272156</t>
         </is>
       </c>
     </row>
@@ -1779,32 +1779,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>88532; 128949</t>
+          <t>90241; 130330</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>140196; 664994</t>
+          <t>94709; 136207</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86377; 124375</t>
+          <t>87501; 125259</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>122362; 164192</t>
+          <t>141652; 175419</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>184693; 240237</t>
+          <t>185125; 243694</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>283550; 938768</t>
+          <t>245849; 297906</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>117386</t>
+          <t>122653</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140879</t>
+          <t>156470</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>258265</t>
+          <t>279123</t>
         </is>
       </c>
     </row>
@@ -1897,32 +1897,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>60488; 93054</t>
+          <t>59295; 93744</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>98760; 135831</t>
+          <t>103616; 142238</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>110466; 152425</t>
+          <t>109956; 149553</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>128280; 157463</t>
+          <t>139770; 172789</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>178193; 230898</t>
+          <t>177661; 229806</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>234619; 281203</t>
+          <t>256646; 306322</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>69396</t>
+          <t>74358</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>85764</t>
+          <t>93851</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>155161</t>
+          <t>168208</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2015,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>44022; 70044</t>
+          <t>42737; 70414</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>57487; 81316</t>
+          <t>61901; 86681</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77853; 113351</t>
+          <t>76583; 112268</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34615; 136207</t>
+          <t>81755; 107047</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>128059; 171893</t>
+          <t>127762; 172200</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>77496; 202603</t>
+          <t>151069; 186773</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>45440</t>
+          <t>48134</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>87450</t>
+          <t>95349</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>132890</t>
+          <t>143483</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>36459; 58607</t>
+          <t>37276; 59188</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>35566; 55280</t>
+          <t>38748; 59698</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>78247; 116780</t>
+          <t>77923; 115662</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>76678; 99025</t>
+          <t>81958; 108025</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>121577; 166839</t>
+          <t>122144; 166222</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>118123; 148980</t>
+          <t>126835; 160660</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>756412</t>
+          <t>534034</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>628769</t>
+          <t>699733</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1385181</t>
+          <t>1233766</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2251,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>450601; 532950</t>
+          <t>447787; 530340</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>535648; 1357470</t>
+          <t>492282; 581716</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>623660; 717621</t>
+          <t>621069; 719257</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>519238; 689500</t>
+          <t>660448; 745858</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1094059; 1227221</t>
+          <t>1093456; 1223456</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1146383; 2120306</t>
+          <t>1170974; 1290464</t>
         </is>
       </c>
     </row>
